--- a/WGRDBESstockCoord/format/SCF/Example1_SCF_v2.xlsx
+++ b/WGRDBESstockCoord/format/SCF/Example1_SCF_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icesit.sharepoint.com/sites/ExpertGroup/WGRDBES-StockCoord/2026 Meeting Documents/04. Working documents/SCF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBESstockCoord/WGRDBESstockCoord/format/SCF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{5341725A-BA8D-4115-B34A-8FD3006C769D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E7246CB-59BE-45C6-B15D-0F8C4937B263}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{5341725A-BA8D-4115-B34A-8FD3006C769D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C2FD86D-D093-45BB-A5A2-F4101B1F1452}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{274BEBFC-7315-4E02-BADA-C86CAB5A4DD1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{274BEBFC-7315-4E02-BADA-C86CAB5A4DD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Catch (CC)" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="46">
   <si>
     <t>year</t>
   </si>
@@ -169,6 +169,15 @@
   </si>
   <si>
     <t>numMeasurements</t>
+  </si>
+  <si>
+    <t>calendarYear</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>yearStartDate</t>
   </si>
 </sst>
 </file>
@@ -586,7 +595,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5BD379EE-A95E-4043-BEF7-D0A5635B2779}" name="Table3" displayName="Table3" ref="C1:K3" totalsRowShown="0" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5BD379EE-A95E-4043-BEF7-D0A5635B2779}" name="Table3" displayName="Table3" ref="E1:M3" totalsRowShown="0" dataDxfId="9">
   <tableColumns count="9">
     <tableColumn id="3" xr3:uid="{EB0C26C2-64D5-42E9-8783-EE9E325B8DB0}" name="year" dataDxfId="8"/>
     <tableColumn id="4" xr3:uid="{F4F27F34-7B9F-432C-A021-9578FFF163E8}" name="workingGroup " dataDxfId="7"/>
@@ -603,9 +612,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EF110A19-58A9-44CF-B725-E50791CD84C4}" name="Table5" displayName="Table5" ref="C1:X17" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:V17">
-    <sortCondition ref="R1:R17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EF110A19-58A9-44CF-B725-E50791CD84C4}" name="Table5" displayName="Table5" ref="D1:Y17" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:W17">
+    <sortCondition ref="S1:S17"/>
   </sortState>
   <tableColumns count="22">
     <tableColumn id="3" xr3:uid="{BA380933-111F-49DD-A7BE-FE6C7F5FFF2F}" name="year" dataDxfId="31"/>
@@ -898,142 +907,213 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031C7378-5F2E-42AD-B8F9-743EB4ADE6CA}">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="5.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.5546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>34</v>
       </c>
       <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="1">
+      <c r="E2" s="1">
         <v>2023</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>17</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>5000</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="1">
+      <c r="E3" s="1">
         <v>2023</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" t="s">
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" t="s">
         <v>27</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>17</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>25000</v>
       </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B4"/>
+      <c r="C4"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B5"/>
+      <c r="C5"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B6"/>
+      <c r="C6"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B7"/>
+      <c r="C7"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B8"/>
+      <c r="C8"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B9"/>
+      <c r="C9"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B10"/>
+      <c r="C10"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B11"/>
+      <c r="C11"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B12"/>
+      <c r="C12"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B13"/>
+      <c r="C13"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B14"/>
+      <c r="C14"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B15"/>
+      <c r="C15"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B16"/>
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17"/>
+      <c r="C17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1046,857 +1126,876 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47BE0360-1F51-48E9-AAF3-D8696FB62C20}">
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="3" width="13.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="1">
+        <v>44</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2" s="1">
         <v>2023</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>2</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="1">
+      <c r="V2" s="1">
         <v>208.69800000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="1">
+        <v>44</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3" s="1">
         <v>2023</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="1">
+      <c r="O3" s="1">
         <v>3</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U3" s="1">
+      <c r="V3" s="1">
         <v>42.3384</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="1">
+        <v>44</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4" s="1">
         <v>2023</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N4" s="1">
+      <c r="O4" s="1">
         <v>4</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U4" s="1">
+      <c r="V4" s="1">
         <v>17.529620000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="1">
+        <v>44</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5" s="1">
         <v>2023</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>5</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U5" s="1">
+      <c r="V5" s="1">
         <v>11.48574</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="1">
+        <v>44</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6" s="1">
         <v>2023</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>2</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="T6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="U6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U6" s="1">
+      <c r="V6" s="1">
         <v>478.71000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="1">
+        <v>44</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7" s="1">
         <v>2023</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>3</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="U7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U7" s="1">
+      <c r="V7" s="1">
         <v>584.97</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="1">
+        <v>44</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8" s="1">
         <v>2023</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>4</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="R8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="S8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="T8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="U8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U8" s="1">
+      <c r="V8" s="1">
         <v>907.98</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="1">
+        <v>44</v>
+      </c>
+      <c r="C9"/>
+      <c r="D9" s="1">
         <v>2023</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>5</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="R9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="U9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U9" s="1">
+      <c r="V9" s="1">
         <v>1290.6899999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="1">
+        <v>44</v>
+      </c>
+      <c r="C10"/>
+      <c r="D10" s="1">
         <v>2023</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <v>2</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T10" s="1" t="s">
+      <c r="U10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="1">
+      <c r="V10" s="1">
         <v>208698</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="1">
+        <v>44</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11" s="1">
         <v>2023</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
         <v>3</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="R11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="S11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="T11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T11" s="1" t="s">
+      <c r="U11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1">
+      <c r="V11" s="1">
         <v>42338</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="1">
+        <v>44</v>
+      </c>
+      <c r="C12"/>
+      <c r="D12" s="1">
         <v>2023</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <v>4</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="Q12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="R12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="T12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T12" s="1" t="s">
+      <c r="U12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1">
+      <c r="V12" s="1">
         <v>17530</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="1">
+        <v>44</v>
+      </c>
+      <c r="C13"/>
+      <c r="D13" s="1">
         <v>2023</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
         <v>5</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="T13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T13" s="1" t="s">
+      <c r="U13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U13" s="1">
+      <c r="V13" s="1">
         <v>11486</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="1">
+        <v>44</v>
+      </c>
+      <c r="C14"/>
+      <c r="D14" s="1">
         <v>2023</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <v>2</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="Q14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="R14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="T14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T14" s="1" t="s">
+      <c r="U14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U14" s="1">
+      <c r="V14" s="1">
         <v>0.47899999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="1">
+        <v>44</v>
+      </c>
+      <c r="C15"/>
+      <c r="D15" s="1">
         <v>2023</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N15" s="1">
+      <c r="O15" s="1">
         <v>3</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="Q15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q15" s="1" t="s">
+      <c r="R15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R15" s="1" t="s">
+      <c r="S15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S15" s="1" t="s">
+      <c r="T15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T15" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U15" s="1">
+      <c r="V15" s="1">
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="1">
+        <v>44</v>
+      </c>
+      <c r="C16"/>
+      <c r="D16" s="1">
         <v>2023</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N16" s="1">
+      <c r="O16" s="1">
         <v>4</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="T16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T16" s="1" t="s">
+      <c r="U16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U16" s="1">
+      <c r="V16" s="1">
         <v>0.90800000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="1">
+        <v>44</v>
+      </c>
+      <c r="C17"/>
+      <c r="D17" s="1">
         <v>2023</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N17" s="1">
+      <c r="O17" s="1">
         <v>5</v>
       </c>
-      <c r="P17" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="R17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S17" s="1" t="s">
+      <c r="T17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T17" s="1" t="s">
+      <c r="U17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U17" s="1">
+      <c r="V17" s="1">
         <v>1.2909999999999999</v>
       </c>
     </row>
@@ -1910,9 +2009,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2060,26 +2162,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF5FD55-8FE0-4218-9C8B-E5F035C6ADC7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46D2B905-AB5A-461F-9589-9E2611C6FC90}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2103,9 +2194,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46D2B905-AB5A-461F-9589-9E2611C6FC90}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF5FD55-8FE0-4218-9C8B-E5F035C6ADC7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WGRDBESstockCoord/format/SCF/Example1_SCF_v2.xlsx
+++ b/WGRDBESstockCoord/format/SCF/Example1_SCF_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBESstockCoord/WGRDBESstockCoord/format/SCF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\Rstudio\D1SCI\VISBIO\RDBESstockCoord\WGRDBESstockCoord\format\SCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="8_{5341725A-BA8D-4115-B34A-8FD3006C769D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C2FD86D-D093-45BB-A5A2-F4101B1F1452}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1753EC07-0C5A-4482-A111-43A9DCC5F0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{274BEBFC-7315-4E02-BADA-C86CAB5A4DD1}"/>
+    <workbookView xWindow="-30615" yWindow="3195" windowWidth="28800" windowHeight="15285" activeTab="1" xr2:uid="{274BEBFC-7315-4E02-BADA-C86CAB5A4DD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Catch (CC)" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="44">
   <si>
     <t>year</t>
   </si>
@@ -157,12 +157,6 @@
   </si>
   <si>
     <t>NE3</t>
-  </si>
-  <si>
-    <t>temporalType</t>
-  </si>
-  <si>
-    <t>Calender</t>
   </si>
   <si>
     <t>numTrips</t>
@@ -232,100 +226,6 @@
     <dxf>
       <font>
         <b val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -581,6 +481,100 @@
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -595,50 +589,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5BD379EE-A95E-4043-BEF7-D0A5635B2779}" name="Table3" displayName="Table3" ref="E1:M3" totalsRowShown="0" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5BD379EE-A95E-4043-BEF7-D0A5635B2779}" name="Table3" displayName="Table3" ref="D1:L3" totalsRowShown="0" dataDxfId="33">
   <tableColumns count="9">
-    <tableColumn id="3" xr3:uid="{EB0C26C2-64D5-42E9-8783-EE9E325B8DB0}" name="year" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{F4F27F34-7B9F-432C-A021-9578FFF163E8}" name="workingGroup " dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{2D8A57EE-EFDE-433E-933C-FF1837F4CD5F}" name="stock" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{ADD8FCEB-6CC8-4199-BCFB-523F7B0801C1}" name="catchCategory" dataDxfId="5"/>
-    <tableColumn id="23" xr3:uid="{932A1E40-E734-4523-8E33-764AB425E93E}" name="seasonType" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{0FC208EF-7705-48EA-BAAB-510461660FBC}" name="seasonValue" dataDxfId="3"/>
-    <tableColumn id="24" xr3:uid="{A0420DBC-4F40-4A80-A651-38D473676560}" name="areaType" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{7F1207FD-19AB-434F-8B1E-C60F5E977803}" name="areaValue" dataDxfId="1"/>
-    <tableColumn id="25" xr3:uid="{F7A303DA-764F-4EA3-8018-4A4BA13128FE}" name="fleetValue" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{EB0C26C2-64D5-42E9-8783-EE9E325B8DB0}" name="year" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{F4F27F34-7B9F-432C-A021-9578FFF163E8}" name="workingGroup " dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{2D8A57EE-EFDE-433E-933C-FF1837F4CD5F}" name="stock" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{ADD8FCEB-6CC8-4199-BCFB-523F7B0801C1}" name="catchCategory" dataDxfId="29"/>
+    <tableColumn id="23" xr3:uid="{932A1E40-E734-4523-8E33-764AB425E93E}" name="seasonType" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{0FC208EF-7705-48EA-BAAB-510461660FBC}" name="seasonValue" dataDxfId="27"/>
+    <tableColumn id="24" xr3:uid="{A0420DBC-4F40-4A80-A651-38D473676560}" name="areaType" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{7F1207FD-19AB-434F-8B1E-C60F5E977803}" name="areaValue" dataDxfId="25"/>
+    <tableColumn id="25" xr3:uid="{F7A303DA-764F-4EA3-8018-4A4BA13128FE}" name="fleetValue" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EF110A19-58A9-44CF-B725-E50791CD84C4}" name="Table5" displayName="Table5" ref="D1:Y17" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EF110A19-58A9-44CF-B725-E50791CD84C4}" name="Table5" displayName="Table5" ref="D1:Y17" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:W17">
     <sortCondition ref="S1:S17"/>
   </sortState>
   <tableColumns count="22">
-    <tableColumn id="3" xr3:uid="{BA380933-111F-49DD-A7BE-FE6C7F5FFF2F}" name="year" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{F0C15844-27B1-45D0-AF69-1BC33D22B785}" name="workingGroup " dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{0135DBB6-FA58-4BD7-B3A0-65A9A54CF06D}" name="stock" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{EC3EE5A9-0859-4658-8463-E9669F8352B8}" name="catchCategory" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{A8FCB00A-6398-447D-8DBE-DDF4BC06B090}" name="seasonType" dataDxfId="27"/>
-    <tableColumn id="18" xr3:uid="{6AB34549-CDC7-4E6E-BD27-29B839D0D5D0}" name="seasonValue" dataDxfId="26"/>
-    <tableColumn id="16" xr3:uid="{987CCC13-CB86-469E-90B9-B37991365629}" name="areaType" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{D6BF8D9F-3336-4655-A30D-8A3004DF1C9F}" name="areaValue" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{0AB9C810-C598-4B9F-AF99-386BA96AB4E2}" name="fleetValue" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{818215D1-5F14-474E-83B6-0B29680543F4}" name="distributionType" dataDxfId="22"/>
-    <tableColumn id="1" xr3:uid="{91280146-22D2-478D-96C9-9967859E34DD}" name="distributionUnit" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{B3627208-1F20-464B-A6A9-029F405D0D58}" name="distributionClass" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{F4642F40-5426-4B4D-80B4-D9C15C6B01FC}" name="ageGroupPlus" dataDxfId="19"/>
-    <tableColumn id="24" xr3:uid="{9ED3275C-5D4D-46B3-8C02-1BA99E49EE43}" name="attributeType" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{8927F130-69A0-4426-A90C-FF32BF739E5E}" name="attributeValue" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{137F0ADC-CCC3-40C3-802C-B921B8CC903B}" name="variableType" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{920A2180-77A0-4DA5-98F6-40B2FC451A1A}" name="variableUnit" dataDxfId="15"/>
-    <tableColumn id="23" xr3:uid="{A3402B3E-5ED3-4CED-97A4-CF067A4DB4A8}" name="valueType" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{8115C967-5761-4112-8FD1-9E078ED40B42}" name="value" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{56848A51-DFDF-4FD6-B189-98767DE533DB}" name="variance" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{8BB62424-A3D0-41C2-9550-DEE6EB32ADF5}" name="numTrips" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{D1FC2E29-95CD-45CD-BB93-897304CA2864}" name="numMeasurements" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{BA380933-111F-49DD-A7BE-FE6C7F5FFF2F}" name="year" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{F0C15844-27B1-45D0-AF69-1BC33D22B785}" name="workingGroup " dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{0135DBB6-FA58-4BD7-B3A0-65A9A54CF06D}" name="stock" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{EC3EE5A9-0859-4658-8463-E9669F8352B8}" name="catchCategory" dataDxfId="18"/>
+    <tableColumn id="19" xr3:uid="{A8FCB00A-6398-447D-8DBE-DDF4BC06B090}" name="seasonType" dataDxfId="17"/>
+    <tableColumn id="18" xr3:uid="{6AB34549-CDC7-4E6E-BD27-29B839D0D5D0}" name="seasonValue" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{987CCC13-CB86-469E-90B9-B37991365629}" name="areaType" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{D6BF8D9F-3336-4655-A30D-8A3004DF1C9F}" name="areaValue" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{0AB9C810-C598-4B9F-AF99-386BA96AB4E2}" name="fleetValue" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{818215D1-5F14-474E-83B6-0B29680543F4}" name="distributionType" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{91280146-22D2-478D-96C9-9967859E34DD}" name="distributionUnit" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{B3627208-1F20-464B-A6A9-029F405D0D58}" name="distributionClass" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{F4642F40-5426-4B4D-80B4-D9C15C6B01FC}" name="ageGroupPlus" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{9ED3275C-5D4D-46B3-8C02-1BA99E49EE43}" name="attributeType" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{8927F130-69A0-4426-A90C-FF32BF739E5E}" name="attributeValue" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{137F0ADC-CCC3-40C3-802C-B921B8CC903B}" name="variableType" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{920A2180-77A0-4DA5-98F6-40B2FC451A1A}" name="variableUnit" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{A3402B3E-5ED3-4CED-97A4-CF067A4DB4A8}" name="valueType" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{8115C967-5761-4112-8FD1-9E078ED40B42}" name="value" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{56848A51-DFDF-4FD6-B189-98767DE533DB}" name="variance" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{8BB62424-A3D0-41C2-9550-DEE6EB32ADF5}" name="numTrips" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{D1FC2E29-95CD-45CD-BB93-897304CA2864}" name="numMeasurements" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -907,207 +901,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031C7378-5F2E-42AD-B8F9-743EB4ADE6CA}">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="13.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="5.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>34</v>
       </c>
       <c r="B1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s">
         <v>43</v>
       </c>
-      <c r="C1" t="s">
-        <v>45</v>
-      </c>
       <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2"/>
-      <c r="D2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="D2" s="1">
         <v>2023</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
       <c r="N2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
         <v>17</v>
       </c>
-      <c r="P2">
+      <c r="O2">
         <v>5000</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3"/>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="1">
         <v>2023</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
       <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
         <v>17</v>
       </c>
-      <c r="P3">
+      <c r="O3">
         <v>25000</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B4"/>
       <c r="C4"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B5"/>
       <c r="C5"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6"/>
       <c r="C6"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B7"/>
       <c r="C7"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8"/>
       <c r="C8"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B9"/>
       <c r="C9"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B10"/>
       <c r="C10"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B11"/>
       <c r="C11"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B12"/>
       <c r="C12"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B13"/>
       <c r="C13"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B14"/>
       <c r="C14"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15"/>
       <c r="C15"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B16"/>
       <c r="C16"/>
     </row>
@@ -1159,10 +1143,10 @@
         <v>34</v>
       </c>
       <c r="B1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" t="s">
-        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -1225,10 +1209,10 @@
         <v>12</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -1236,7 +1220,7 @@
         <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2"/>
       <c r="D2" s="1">
@@ -1284,7 +1268,7 @@
         <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3"/>
       <c r="D3" s="1">
@@ -1332,7 +1316,7 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4"/>
       <c r="D4" s="1">
@@ -1380,7 +1364,7 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C5"/>
       <c r="D5" s="1">
@@ -1428,7 +1412,7 @@
         <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C6"/>
       <c r="D6" s="1">
@@ -1476,7 +1460,7 @@
         <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7"/>
       <c r="D7" s="1">
@@ -1524,7 +1508,7 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8"/>
       <c r="D8" s="1">
@@ -1572,7 +1556,7 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9"/>
       <c r="D9" s="1">
@@ -1620,7 +1604,7 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10"/>
       <c r="D10" s="1">
@@ -1668,7 +1652,7 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11"/>
       <c r="D11" s="1">
@@ -1716,7 +1700,7 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12"/>
       <c r="D12" s="1">
@@ -1764,7 +1748,7 @@
         <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13"/>
       <c r="D13" s="1">
@@ -1812,7 +1796,7 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C14"/>
       <c r="D14" s="1">
@@ -1860,7 +1844,7 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15"/>
       <c r="D15" s="1">
@@ -1908,7 +1892,7 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16"/>
       <c r="D16" s="1">
@@ -1956,7 +1940,7 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17"/>
       <c r="D17" s="1">
@@ -2018,6 +2002,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CF5149A2F9434B4282E37FA76C9DDAE3" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9daeb8933c56b40f3271bb867fbbc8d8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a657112-7d30-43e0-84e9-071e428c6b63" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d201b2d4740b92ddb00486e196a42d19" ns2:_="">
     <xsd:import namespace="9a657112-7d30-43e0-84e9-071e428c6b63"/>
@@ -2161,12 +2151,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46D2B905-AB5A-461F-9589-9E2611C6FC90}">
   <ds:schemaRefs>
@@ -2176,6 +2160,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF5FD55-8FE0-4218-9C8B-E5F035C6ADC7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E39FD15-24FF-4E00-8189-DD6FFAF9F3C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2191,20 +2191,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF5FD55-8FE0-4218-9C8B-E5F035C6ADC7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>